--- a/docs/kansensho_2026-10.xlsx
+++ b/docs/kansensho_2026-10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y-miy\Dropbox\AI作業場\感染症\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39BA5EA-D656-4C34-8862-6374146AB349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D41E4C-A4A9-411C-BC99-60B0BAA23277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7383" uniqueCount="2889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7383" uniqueCount="2888">
   <si>
     <t>世界の感染症と日本の水際対策：HIV/エイズ・梅毒・はしか・結核</t>
   </si>
@@ -6993,7 +6993,7 @@
     <t>https://www.mhlw.go.jp/content/10900000/001678695.xlsx</t>
   </si>
   <si>
-    <t>2026-03-24（Excelファイルの更新日時。掲載ページ https://www.mhlw.go.jp/topics/2005/04/tp0411-1.html に日付表示なし）</t>
+    <t>2026-03-24（Excelファイルの更新日時。掲載ページ https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/kenkou_iryou/kenkou/kekkaku-kansenshou/seikansenshou/houkokusuu.html に日付表示なし）</t>
   </si>
   <si>
     <t>感染症法に基づく梅毒の届出状況2024年（2025年11月15日現在）</t>
@@ -7413,9 +7413,6 @@
     <t>二国間取決め（技能実習の協力覚書）</t>
   </si>
   <si>
-    <t>https://www.otit.go.jp/soushutsu_nikokukan/</t>
-  </si>
-  <si>
     <t>世界-6</t>
   </si>
   <si>
@@ -7647,7 +7644,7 @@
     <t>Global Health Observatory：梅毒（妊婦健診で梅毒が陽性だった割合・報告された梅毒の数・先天梅毒の率。各国の報告）</t>
   </si>
   <si>
-    <t>https://www.who.int/data/gho/data/themes/topics/sexually-transmitted-infections</t>
+    <t>https://www.who.int/data/gho/data/themes/topics/data-on-syphilis</t>
   </si>
   <si>
     <t>2026-10-26確認</t>
@@ -20002,7 +19999,7 @@
         <v>2152</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>2449</v>
+        <v>2155</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>2291</v>
@@ -20013,13 +20010,13 @@
     </row>
     <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="22" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="B68" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>2062</v>
@@ -20028,7 +20025,7 @@
         <v>2163</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="G68" s="22" t="s">
         <v>2256</v>
@@ -20036,13 +20033,13 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="22" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="B69" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>2062</v>
@@ -20051,7 +20048,7 @@
         <v>2159</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="G69" s="22" t="s">
         <v>2256</v>
@@ -20059,19 +20056,19 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="22" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="B70" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>2456</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>2457</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="23" t="s">
         <v>2458</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>2459</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>2291</v>
@@ -20082,22 +20079,22 @@
     </row>
     <row r="71" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="22" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="B71" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E71" s="23" t="s">
         <v>2461</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>2458</v>
-      </c>
-      <c r="E71" s="23" t="s">
+      <c r="F71" s="3" t="s">
         <v>2462</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>2463</v>
       </c>
       <c r="G71" s="22" t="s">
         <v>2256</v>
@@ -20105,19 +20102,19 @@
     </row>
     <row r="72" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="22" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B72" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>2465</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="E72" s="23" t="s">
         <v>2466</v>
-      </c>
-      <c r="E72" s="23" t="s">
-        <v>2467</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>2291</v>
@@ -20128,22 +20125,22 @@
     </row>
     <row r="73" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="22" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>2465</v>
+      </c>
+      <c r="E73" s="23" t="s">
         <v>2469</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>2466</v>
-      </c>
-      <c r="E73" s="23" t="s">
+      <c r="F73" s="3" t="s">
         <v>2470</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>2471</v>
       </c>
       <c r="G73" s="22" t="s">
         <v>2256</v>
@@ -20151,22 +20148,22 @@
     </row>
     <row r="74" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="22" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="B74" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>2098</v>
       </c>
       <c r="E74" s="23" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>2474</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>2475</v>
       </c>
       <c r="G74" s="22" t="s">
         <v>2256</v>
@@ -20174,19 +20171,19 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="22" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B75" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>2131</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>2291</v>
@@ -20197,19 +20194,19 @@
     </row>
     <row r="76" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="22" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="B76" s="22" t="s">
         <v>2221</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>2291</v>
@@ -20223,19 +20220,19 @@
         <v>906</v>
       </c>
       <c r="B77" s="22" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>2482</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="D77" s="3" t="s">
         <v>2483</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="E77" s="23" t="s">
         <v>2484</v>
       </c>
-      <c r="E77" s="23" t="s">
+      <c r="F77" s="3" t="s">
         <v>2485</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>2486</v>
       </c>
       <c r="G77" s="22" t="s">
         <v>2256</v>
@@ -20246,7 +20243,7 @@
         <v>914</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>2194</v>
@@ -20258,7 +20255,7 @@
         <v>2198</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="G78" s="22" t="s">
         <v>2256</v>
@@ -20266,19 +20263,19 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="22" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>2488</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>2482</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>2489</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>2291</v>
@@ -20289,19 +20286,19 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="22" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>2491</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>2482</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>2492</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>2291</v>
@@ -20315,19 +20312,19 @@
         <v>901</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E81" s="23" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>2495</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>2496</v>
       </c>
       <c r="G81" s="22" t="s">
         <v>2256</v>
@@ -20338,19 +20335,19 @@
         <v>897</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>2497</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="E82" s="23" t="s">
         <v>2498</v>
       </c>
-      <c r="E82" s="23" t="s">
+      <c r="F82" s="3" t="s">
         <v>2499</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>2500</v>
       </c>
       <c r="G82" s="22" t="s">
         <v>2256</v>
@@ -20358,22 +20355,22 @@
     </row>
     <row r="83" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="22" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>2501</v>
       </c>
-      <c r="B83" s="22" t="s">
-        <v>2482</v>
-      </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>2502</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="E83" s="23" t="s">
         <v>2503</v>
       </c>
-      <c r="E83" s="23" t="s">
+      <c r="F83" s="3" t="s">
         <v>2504</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>2505</v>
       </c>
       <c r="G83" s="22" t="s">
         <v>2256</v>
@@ -20384,16 +20381,16 @@
         <v>910</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>2291</v>
@@ -20404,22 +20401,22 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="22" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>2508</v>
       </c>
-      <c r="B85" s="22" t="s">
-        <v>2482</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>2509</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="E85" s="23" t="s">
         <v>2510</v>
       </c>
-      <c r="E85" s="23" t="s">
+      <c r="F85" s="3" t="s">
         <v>2511</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>2512</v>
       </c>
       <c r="G85" s="22" t="s">
         <v>2256</v>
@@ -20427,13 +20424,13 @@
     </row>
     <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="22" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B86" s="22" t="s">
         <v>2513</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="C86" s="3" t="s">
         <v>2514</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>2515</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>2093</v>
@@ -20442,7 +20439,7 @@
         <v>2105</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="G86" s="22" t="s">
         <v>2256</v>
@@ -20450,22 +20447,22 @@
     </row>
     <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="22" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>2513</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>2517</v>
-      </c>
-      <c r="B87" s="22" t="s">
-        <v>2514</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>2518</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E87" s="23" t="s">
+        <v>2518</v>
+      </c>
+      <c r="F87" s="3" t="s">
         <v>2519</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>2520</v>
       </c>
       <c r="G87" s="22" t="s">
         <v>2256</v>
@@ -20473,22 +20470,22 @@
     </row>
     <row r="88" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="22" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B88" s="22" t="s">
+        <v>2513</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>2521</v>
       </c>
-      <c r="B88" s="22" t="s">
-        <v>2514</v>
-      </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>2522</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="E88" s="23" t="s">
         <v>2523</v>
       </c>
-      <c r="E88" s="23" t="s">
-        <v>2524</v>
-      </c>
       <c r="F88" s="3" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="G88" s="22" t="s">
         <v>2256</v>
@@ -20496,22 +20493,22 @@
     </row>
     <row r="89" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="22" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>2513</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>2525</v>
-      </c>
-      <c r="B89" s="22" t="s">
-        <v>2514</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>2526</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E89" s="23" t="s">
+        <v>2526</v>
+      </c>
+      <c r="F89" s="3" t="s">
         <v>2527</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>2528</v>
       </c>
       <c r="G89" s="22" t="s">
         <v>2256</v>
@@ -20519,19 +20516,19 @@
     </row>
     <row r="90" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="22" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>2513</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>2529</v>
       </c>
-      <c r="B90" s="22" t="s">
-        <v>2514</v>
-      </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="3" t="s">
         <v>2530</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="E90" s="23" t="s">
         <v>2531</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>2532</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>2291</v>
@@ -20545,10 +20542,10 @@
         <v>654</v>
       </c>
       <c r="B91" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>2533</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>2534</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>2131</v>
@@ -20557,7 +20554,7 @@
         <v>2142</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="G91" s="22" t="s">
         <v>2256</v>
@@ -20565,19 +20562,19 @@
     </row>
     <row r="92" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="22" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>2536</v>
-      </c>
-      <c r="B92" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>2537</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>2152</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>2449</v>
+        <v>2155</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>2291</v>
@@ -20588,19 +20585,19 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="22" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>2538</v>
-      </c>
-      <c r="B93" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>2539</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E93" s="23" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>2291</v>
@@ -20611,19 +20608,19 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="22" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>2541</v>
-      </c>
-      <c r="B94" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>2542</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>2131</v>
       </c>
       <c r="E94" s="23" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>2291</v>
@@ -20634,19 +20631,19 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="22" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>2543</v>
-      </c>
-      <c r="B95" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>2544</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>2291</v>
@@ -20657,19 +20654,19 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="22" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>2546</v>
-      </c>
-      <c r="B96" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>2547</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>2152</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>2291</v>
@@ -20680,22 +20677,22 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="22" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>2549</v>
-      </c>
-      <c r="B97" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>2550</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E97" s="23" t="s">
+        <v>2550</v>
+      </c>
+      <c r="F97" s="3" t="s">
         <v>2551</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>2552</v>
       </c>
       <c r="G97" s="22" t="s">
         <v>2256</v>
@@ -20703,13 +20700,13 @@
     </row>
     <row r="98" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="22" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>2062</v>
@@ -20718,7 +20715,7 @@
         <v>2163</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="G98" s="22" t="s">
         <v>2256</v>
@@ -20726,22 +20723,22 @@
     </row>
     <row r="99" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="22" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>2555</v>
       </c>
-      <c r="B99" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="3" t="s">
         <v>2556</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="E99" s="23" t="s">
         <v>2557</v>
       </c>
-      <c r="E99" s="23" t="s">
+      <c r="F99" s="3" t="s">
         <v>2558</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>2559</v>
       </c>
       <c r="G99" s="22" t="s">
         <v>2256</v>
@@ -20749,22 +20746,22 @@
     </row>
     <row r="100" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="22" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B100" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>2560</v>
-      </c>
-      <c r="B100" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>2561</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E100" s="23" t="s">
+        <v>2561</v>
+      </c>
+      <c r="F100" s="3" t="s">
         <v>2562</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>2563</v>
       </c>
       <c r="G100" s="22" t="s">
         <v>2256</v>
@@ -20772,22 +20769,22 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="22" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B101" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>2564</v>
-      </c>
-      <c r="B101" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>2565</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E101" s="23" t="s">
+        <v>2565</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>2566</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>2567</v>
       </c>
       <c r="G101" s="22" t="s">
         <v>2256</v>
@@ -20795,13 +20792,13 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="22" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B102" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>2568</v>
-      </c>
-      <c r="B102" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>2569</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>2062</v>
@@ -20810,7 +20807,7 @@
         <v>2159</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="G102" s="22" t="s">
         <v>2256</v>
@@ -20818,22 +20815,22 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="22" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B103" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>2571</v>
-      </c>
-      <c r="B103" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>2572</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E103" s="23" t="s">
+        <v>2572</v>
+      </c>
+      <c r="F103" s="3" t="s">
         <v>2573</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>2574</v>
       </c>
       <c r="G103" s="22" t="s">
         <v>2256</v>
@@ -20841,22 +20838,22 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="22" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B104" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>2575</v>
-      </c>
-      <c r="B104" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>2576</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>2131</v>
       </c>
       <c r="E104" s="23" t="s">
+        <v>2576</v>
+      </c>
+      <c r="F104" s="3" t="s">
         <v>2577</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>2578</v>
       </c>
       <c r="G104" s="22" t="s">
         <v>2256</v>
@@ -20864,22 +20861,22 @@
     </row>
     <row r="105" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="22" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B105" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>2579</v>
-      </c>
-      <c r="B105" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>2580</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>2131</v>
       </c>
       <c r="E105" s="23" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F105" s="3" t="s">
         <v>2581</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>2582</v>
       </c>
       <c r="G105" s="22" t="s">
         <v>2256</v>
@@ -20887,19 +20884,19 @@
     </row>
     <row r="106" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="22" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B106" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>2583</v>
-      </c>
-      <c r="B106" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>2584</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>2131</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>2291</v>
@@ -20910,22 +20907,22 @@
     </row>
     <row r="107" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="22" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B107" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>2586</v>
       </c>
-      <c r="B107" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="3" t="s">
         <v>2587</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="E107" s="23" t="s">
         <v>2588</v>
       </c>
-      <c r="E107" s="23" t="s">
+      <c r="F107" s="3" t="s">
         <v>2589</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>2590</v>
       </c>
       <c r="G107" s="22" t="s">
         <v>2256</v>
@@ -20933,19 +20930,19 @@
     </row>
     <row r="108" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="22" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B108" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>2591</v>
-      </c>
-      <c r="B108" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>2592</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>2152</v>
       </c>
       <c r="E108" s="23" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>2291</v>
@@ -20956,22 +20953,22 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="22" t="s">
+        <v>2593</v>
+      </c>
+      <c r="B109" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>2594</v>
-      </c>
-      <c r="B109" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>2595</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>2152</v>
       </c>
       <c r="E109" s="23" t="s">
+        <v>2595</v>
+      </c>
+      <c r="F109" s="3" t="s">
         <v>2596</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>2597</v>
       </c>
       <c r="G109" s="22" t="s">
         <v>2256</v>
@@ -20979,22 +20976,22 @@
     </row>
     <row r="110" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="22" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B110" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>2598</v>
       </c>
-      <c r="B110" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C110" s="3" t="s">
+      <c r="D110" s="3" t="s">
+        <v>2587</v>
+      </c>
+      <c r="E110" s="23" t="s">
         <v>2599</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>2588</v>
-      </c>
-      <c r="E110" s="23" t="s">
+      <c r="F110" s="3" t="s">
         <v>2600</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>2601</v>
       </c>
       <c r="G110" s="22" t="s">
         <v>2256</v>
@@ -21002,22 +20999,22 @@
     </row>
     <row r="111" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="22" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B111" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>2602</v>
-      </c>
-      <c r="B111" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>2603</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>2152</v>
       </c>
       <c r="E111" s="23" t="s">
+        <v>2603</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>2604</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>2605</v>
       </c>
       <c r="G111" s="22" t="s">
         <v>2256</v>
@@ -21025,19 +21022,19 @@
     </row>
     <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="22" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B112" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>2606</v>
-      </c>
-      <c r="B112" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>2607</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>2131</v>
       </c>
       <c r="E112" s="23" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>2291</v>
@@ -21048,22 +21045,22 @@
     </row>
     <row r="113" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="22" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B113" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>2609</v>
       </c>
-      <c r="B113" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E113" s="23" t="s">
         <v>2610</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="E113" s="23" t="s">
+      <c r="F113" s="3" t="s">
         <v>2611</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>2612</v>
       </c>
       <c r="G113" s="22" t="s">
         <v>2256</v>
@@ -21071,22 +21068,22 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="22" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B114" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>2613</v>
       </c>
-      <c r="B114" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>2614</v>
-      </c>
       <c r="D114" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E114" s="23" t="s">
         <v>2484</v>
       </c>
-      <c r="E114" s="23" t="s">
-        <v>2485</v>
-      </c>
       <c r="F114" s="3" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="G114" s="22" t="s">
         <v>2256</v>
@@ -21094,22 +21091,22 @@
     </row>
     <row r="115" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="22" t="s">
+        <v>2614</v>
+      </c>
+      <c r="B115" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>2615</v>
       </c>
-      <c r="B115" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E115" s="23" t="s">
         <v>2616</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="E115" s="23" t="s">
+      <c r="F115" s="3" t="s">
         <v>2617</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>2618</v>
       </c>
       <c r="G115" s="22" t="s">
         <v>2256</v>
@@ -21117,22 +21114,22 @@
     </row>
     <row r="116" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="22" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B116" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>2619</v>
       </c>
-      <c r="B116" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E116" s="23" t="s">
         <v>2620</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="E116" s="23" t="s">
+      <c r="F116" s="3" t="s">
         <v>2621</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>2622</v>
       </c>
       <c r="G116" s="22" t="s">
         <v>2256</v>
@@ -21140,19 +21137,19 @@
     </row>
     <row r="117" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="22" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B117" s="22" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>2623</v>
-      </c>
-      <c r="B117" s="22" t="s">
-        <v>2533</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>2624</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>2291</v>
@@ -21169,16 +21166,16 @@
         <v>1280</v>
       </c>
       <c r="C118" s="3" t="s">
+        <v>2625</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>2626</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="E118" s="23" t="s">
         <v>2627</v>
       </c>
-      <c r="E118" s="23" t="s">
+      <c r="F118" s="3" t="s">
         <v>2628</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>2629</v>
       </c>
       <c r="G118" s="22" t="s">
         <v>2256</v>
@@ -21186,22 +21183,22 @@
     </row>
     <row r="119" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="22" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="B119" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E119" s="23" t="s">
+        <v>2631</v>
+      </c>
+      <c r="F119" s="3" t="s">
         <v>2632</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>2633</v>
       </c>
       <c r="G119" s="22" t="s">
         <v>2256</v>
@@ -21209,22 +21206,22 @@
     </row>
     <row r="120" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="22" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="B120" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E120" s="23" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>2636</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>2637</v>
       </c>
       <c r="G120" s="22" t="s">
         <v>2256</v>
@@ -21238,16 +21235,16 @@
         <v>1280</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E121" s="23" t="s">
+        <v>2638</v>
+      </c>
+      <c r="F121" s="3" t="s">
         <v>2639</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>2640</v>
       </c>
       <c r="G121" s="22" t="s">
         <v>2256</v>
@@ -21255,22 +21252,22 @@
     </row>
     <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="22" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="B122" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E122" s="23" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="G122" s="22" t="s">
         <v>2256</v>
@@ -21278,22 +21275,22 @@
     </row>
     <row r="123" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="22" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="B123" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C123" s="3" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>2645</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="E123" s="23" t="s">
         <v>2646</v>
       </c>
-      <c r="E123" s="23" t="s">
+      <c r="F123" s="3" t="s">
         <v>2647</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>2648</v>
       </c>
       <c r="G123" s="22" t="s">
         <v>2256</v>
@@ -21307,16 +21304,16 @@
         <v>1280</v>
       </c>
       <c r="C124" s="3" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>2649</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="E124" s="23" t="s">
         <v>2650</v>
       </c>
-      <c r="E124" s="23" t="s">
+      <c r="F124" s="3" t="s">
         <v>2651</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>2652</v>
       </c>
       <c r="G124" s="22" t="s">
         <v>2256</v>
@@ -21324,22 +21321,22 @@
     </row>
     <row r="125" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="22" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="B125" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C125" s="3" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>2654</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="E125" s="23" t="s">
         <v>2655</v>
       </c>
-      <c r="E125" s="23" t="s">
-        <v>2656</v>
-      </c>
       <c r="F125" s="3" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="G125" s="22" t="s">
         <v>2256</v>
@@ -21347,22 +21344,22 @@
     </row>
     <row r="126" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="22" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="B126" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>2165</v>
       </c>
       <c r="E126" s="23" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F126" s="3" t="s">
         <v>2659</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>2660</v>
       </c>
       <c r="G126" s="22" t="s">
         <v>2256</v>
@@ -21370,22 +21367,22 @@
     </row>
     <row r="127" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="22" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="B127" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C127" s="3" t="s">
+        <v>2661</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>2662</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="E127" s="23" t="s">
         <v>2663</v>
       </c>
-      <c r="E127" s="23" t="s">
+      <c r="F127" s="3" t="s">
         <v>2664</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>2665</v>
       </c>
       <c r="G127" s="22" t="s">
         <v>2256</v>
@@ -21393,22 +21390,22 @@
     </row>
     <row r="128" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="22" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="B128" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E128" s="23" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>2495</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>2496</v>
       </c>
       <c r="G128" s="22" t="s">
         <v>2256</v>
@@ -21416,22 +21413,22 @@
     </row>
     <row r="129" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="22" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="B129" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C129" s="3" t="s">
+        <v>2668</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E129" s="23" t="s">
         <v>2669</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="E129" s="23" t="s">
-        <v>2670</v>
-      </c>
       <c r="F129" s="3" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="G129" s="22" t="s">
         <v>2256</v>
@@ -21439,22 +21436,22 @@
     </row>
     <row r="130" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="22" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="B130" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="D130" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E130" s="23" t="s">
         <v>2484</v>
       </c>
-      <c r="E130" s="23" t="s">
+      <c r="F130" s="3" t="s">
         <v>2485</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>2486</v>
       </c>
       <c r="G130" s="22" t="s">
         <v>2256</v>
@@ -21468,16 +21465,16 @@
         <v>1280</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E131" s="23" t="s">
+        <v>2673</v>
+      </c>
+      <c r="F131" s="3" t="s">
         <v>2674</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>2675</v>
       </c>
       <c r="G131" s="22" t="s">
         <v>2256</v>
@@ -21485,22 +21482,22 @@
     </row>
     <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="22" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="B132" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E132" s="23" t="s">
+        <v>2677</v>
+      </c>
+      <c r="F132" s="3" t="s">
         <v>2678</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>2679</v>
       </c>
       <c r="G132" s="22" t="s">
         <v>2256</v>
@@ -21514,16 +21511,16 @@
         <v>1280</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E133" s="23" t="s">
+        <v>2680</v>
+      </c>
+      <c r="F133" s="3" t="s">
         <v>2681</v>
-      </c>
-      <c r="F133" s="3" t="s">
-        <v>2682</v>
       </c>
       <c r="G133" s="22" t="s">
         <v>2256</v>
@@ -21537,16 +21534,16 @@
         <v>1280</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E134" s="23" t="s">
+        <v>2683</v>
+      </c>
+      <c r="F134" s="3" t="s">
         <v>2684</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>2685</v>
       </c>
       <c r="G134" s="22" t="s">
         <v>2256</v>
@@ -21554,13 +21551,13 @@
     </row>
     <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="22" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="B135" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>2062</v>
@@ -21569,7 +21566,7 @@
         <v>2397</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="G135" s="22" t="s">
         <v>2256</v>
@@ -21577,22 +21574,22 @@
     </row>
     <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="22" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="B136" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C136" s="3" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D136" s="3" t="s">
         <v>2690</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="E136" s="23" t="s">
         <v>2691</v>
       </c>
-      <c r="E136" s="23" t="s">
+      <c r="F136" s="3" t="s">
         <v>2692</v>
-      </c>
-      <c r="F136" s="3" t="s">
-        <v>2693</v>
       </c>
       <c r="G136" s="22" t="s">
         <v>2256</v>
@@ -21600,22 +21597,22 @@
     </row>
     <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="22" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="B137" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C137" s="3" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="E137" s="23" t="s">
         <v>2695</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="E137" s="23" t="s">
+      <c r="F137" s="3" t="s">
         <v>2696</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>2697</v>
       </c>
       <c r="G137" s="22" t="s">
         <v>2256</v>
@@ -21623,22 +21620,22 @@
     </row>
     <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="22" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="B138" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C138" s="3" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>2699</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="E138" s="23" t="s">
         <v>2700</v>
       </c>
-      <c r="E138" s="23" t="s">
+      <c r="F138" s="3" t="s">
         <v>2701</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>2702</v>
       </c>
       <c r="G138" s="22" t="s">
         <v>2256</v>
@@ -21646,13 +21643,13 @@
     </row>
     <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="22" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="B139" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>2062</v>
@@ -21675,16 +21672,16 @@
         <v>1280</v>
       </c>
       <c r="C140" s="3" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D140" s="3" t="s">
         <v>2705</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="E140" s="23" t="s">
         <v>2706</v>
       </c>
-      <c r="E140" s="23" t="s">
+      <c r="F140" s="3" t="s">
         <v>2707</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>2708</v>
       </c>
       <c r="G140" s="22" t="s">
         <v>2256</v>
@@ -21692,7 +21689,7 @@
     </row>
     <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="22" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="B141" s="22" t="s">
         <v>1280</v>
@@ -21707,7 +21704,7 @@
         <v>2198</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="G141" s="22" t="s">
         <v>2256</v>
@@ -21721,7 +21718,7 @@
         <v>1280</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>2062</v>
@@ -21738,22 +21735,22 @@
     </row>
     <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="22" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="B143" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C143" s="3" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D143" s="3" t="s">
         <v>2712</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="E143" s="23" t="s">
         <v>2713</v>
       </c>
-      <c r="E143" s="23" t="s">
+      <c r="F143" s="3" t="s">
         <v>2714</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>2715</v>
       </c>
       <c r="G143" s="22" t="s">
         <v>2256</v>
@@ -21767,16 +21764,16 @@
         <v>1280</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="D144" s="3" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E144" s="23" t="s">
         <v>2503</v>
       </c>
-      <c r="E144" s="23" t="s">
+      <c r="F144" s="3" t="s">
         <v>2504</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>2505</v>
       </c>
       <c r="G144" s="22" t="s">
         <v>2256</v>
@@ -21790,7 +21787,7 @@
         <v>1280</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>2062</v>
@@ -21799,7 +21796,7 @@
         <v>2391</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="G145" s="22" t="s">
         <v>2256</v>
@@ -21813,16 +21810,16 @@
         <v>1280</v>
       </c>
       <c r="C146" s="3" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E146" s="23" t="s">
         <v>2719</v>
       </c>
-      <c r="D146" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="E146" s="23" t="s">
-        <v>2720</v>
-      </c>
       <c r="F146" s="3" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="G146" s="22" t="s">
         <v>2256</v>
@@ -21830,19 +21827,19 @@
     </row>
     <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="22" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="B147" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>2291</v>
@@ -21853,19 +21850,19 @@
     </row>
     <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="22" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="B148" s="22" t="s">
         <v>1280</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>2291</v>
@@ -21879,7 +21876,7 @@
         <v>1715</v>
       </c>
       <c r="B149" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>2289</v>
@@ -21891,7 +21888,7 @@
         <v>2290</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="G149" s="22" t="s">
         <v>2256</v>
@@ -21902,19 +21899,19 @@
         <v>1738</v>
       </c>
       <c r="B150" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C150" s="3" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D150" s="3" t="s">
         <v>2727</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="E150" s="23" t="s">
         <v>2728</v>
       </c>
-      <c r="E150" s="23" t="s">
+      <c r="F150" s="3" t="s">
         <v>2729</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>2730</v>
       </c>
       <c r="G150" s="22" t="s">
         <v>2256</v>
@@ -21925,19 +21922,19 @@
         <v>1712</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C151" s="3" t="s">
+        <v>2730</v>
+      </c>
+      <c r="D151" s="3" t="s">
         <v>2731</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="E151" s="23" t="s">
         <v>2732</v>
       </c>
-      <c r="E151" s="23" t="s">
+      <c r="F151" s="3" t="s">
         <v>2733</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>2734</v>
       </c>
       <c r="G151" s="22" t="s">
         <v>2256</v>
@@ -21948,19 +21945,19 @@
         <v>1731</v>
       </c>
       <c r="B152" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C152" s="3" t="s">
+        <v>2734</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>2731</v>
+      </c>
+      <c r="E152" s="23" t="s">
         <v>2735</v>
       </c>
-      <c r="D152" s="3" t="s">
-        <v>2732</v>
-      </c>
-      <c r="E152" s="23" t="s">
+      <c r="F152" s="3" t="s">
         <v>2736</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>2737</v>
       </c>
       <c r="G152" s="22" t="s">
         <v>2256</v>
@@ -21968,22 +21965,22 @@
     </row>
     <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="22" t="s">
+        <v>2737</v>
+      </c>
+      <c r="B153" s="22" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>2738</v>
-      </c>
-      <c r="B153" s="22" t="s">
-        <v>2725</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>2739</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E153" s="23" t="s">
+        <v>2739</v>
+      </c>
+      <c r="F153" s="3" t="s">
         <v>2740</v>
-      </c>
-      <c r="F153" s="3" t="s">
-        <v>2741</v>
       </c>
       <c r="G153" s="22" t="s">
         <v>2256</v>
@@ -21994,19 +21991,19 @@
         <v>1772</v>
       </c>
       <c r="B154" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C154" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D154" s="3" t="s">
         <v>2742</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="E154" s="23" t="s">
         <v>2743</v>
       </c>
-      <c r="E154" s="23" t="s">
+      <c r="F154" s="3" t="s">
         <v>2744</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>2745</v>
       </c>
       <c r="G154" s="22" t="s">
         <v>2256</v>
@@ -22017,7 +22014,7 @@
         <v>1722</v>
       </c>
       <c r="B155" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>2439</v>
@@ -22029,7 +22026,7 @@
         <v>2440</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="G155" s="22" t="s">
         <v>2256</v>
@@ -22040,7 +22037,7 @@
         <v>1762</v>
       </c>
       <c r="B156" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>2257</v>
@@ -22063,19 +22060,19 @@
         <v>1734</v>
       </c>
       <c r="B157" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C157" s="3" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D157" s="3" t="s">
         <v>2747</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="E157" s="23" t="s">
         <v>2748</v>
       </c>
-      <c r="E157" s="23" t="s">
+      <c r="F157" s="3" t="s">
         <v>2749</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>2750</v>
       </c>
       <c r="G157" s="22" t="s">
         <v>2256</v>
@@ -22086,7 +22083,7 @@
         <v>1785</v>
       </c>
       <c r="B158" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>528</v>
@@ -22098,7 +22095,7 @@
         <v>2332</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="G158" s="22" t="s">
         <v>2256</v>
@@ -22109,10 +22106,10 @@
         <v>1798</v>
       </c>
       <c r="B159" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>2062</v>
@@ -22132,19 +22129,19 @@
         <v>1789</v>
       </c>
       <c r="B160" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>528</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="E160" s="23" t="s">
+        <v>2751</v>
+      </c>
+      <c r="F160" s="3" t="s">
         <v>2752</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>2753</v>
       </c>
       <c r="G160" s="22" t="s">
         <v>2256</v>
@@ -22155,19 +22152,19 @@
         <v>1782</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E161" s="23" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F161" s="3" t="s">
         <v>2714</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>2715</v>
       </c>
       <c r="G161" s="22" t="s">
         <v>2256</v>
@@ -22178,19 +22175,19 @@
         <v>1795</v>
       </c>
       <c r="B162" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E162" s="23" t="s">
+        <v>2755</v>
+      </c>
+      <c r="F162" s="3" t="s">
         <v>2756</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>2757</v>
       </c>
       <c r="G162" s="22" t="s">
         <v>2256</v>
@@ -22201,19 +22198,19 @@
         <v>1815</v>
       </c>
       <c r="B163" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E163" s="23" t="s">
+        <v>2758</v>
+      </c>
+      <c r="F163" s="3" t="s">
         <v>2759</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>2760</v>
       </c>
       <c r="G163" s="22" t="s">
         <v>2256</v>
@@ -22224,10 +22221,10 @@
         <v>1825</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>2067</v>
@@ -22236,7 +22233,7 @@
         <v>2318</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="G164" s="22" t="s">
         <v>2256</v>
@@ -22247,10 +22244,10 @@
         <v>1827</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>2311</v>
@@ -22259,7 +22256,7 @@
         <v>2335</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="G165" s="22" t="s">
         <v>2256</v>
@@ -22270,19 +22267,19 @@
         <v>1829</v>
       </c>
       <c r="B166" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E166" s="23" t="s">
+        <v>2765</v>
+      </c>
+      <c r="F166" s="3" t="s">
         <v>2766</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>2767</v>
       </c>
       <c r="G166" s="22" t="s">
         <v>2256</v>
@@ -22293,10 +22290,10 @@
         <v>1852</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>2062</v>
@@ -22305,7 +22302,7 @@
         <v>2391</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="G167" s="22" t="s">
         <v>2256</v>
@@ -22316,16 +22313,16 @@
         <v>1847</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E168" s="23" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>2291</v>
@@ -22339,19 +22336,19 @@
         <v>1866</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C169" s="3" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E169" s="23" t="s">
         <v>2772</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>2728</v>
-      </c>
-      <c r="E169" s="23" t="s">
-        <v>2773</v>
-      </c>
       <c r="F169" s="3" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="G169" s="22" t="s">
         <v>2256</v>
@@ -22362,7 +22359,7 @@
         <v>1868</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>2378</v>
@@ -22385,13 +22382,13 @@
         <v>1897</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C171" s="3" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D171" s="3" t="s">
         <v>2774</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>2775</v>
       </c>
       <c r="E171" s="23" t="s">
         <v>2353</v>
@@ -22408,10 +22405,10 @@
         <v>1904</v>
       </c>
       <c r="B172" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>2067</v>
@@ -22431,10 +22428,10 @@
         <v>1900</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>2067</v>
@@ -22443,7 +22440,7 @@
         <v>2364</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="G173" s="22" t="s">
         <v>2256</v>
@@ -22454,19 +22451,19 @@
         <v>1863</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E174" s="23" t="s">
+        <v>2779</v>
+      </c>
+      <c r="F174" s="3" t="s">
         <v>2780</v>
-      </c>
-      <c r="F174" s="3" t="s">
-        <v>2781</v>
       </c>
       <c r="G174" s="22" t="s">
         <v>2256</v>
@@ -22477,19 +22474,19 @@
         <v>1860</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E175" s="23" t="s">
+        <v>2782</v>
+      </c>
+      <c r="F175" s="3" t="s">
         <v>2783</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>2784</v>
       </c>
       <c r="G175" s="22" t="s">
         <v>2256</v>
@@ -22497,22 +22494,22 @@
     </row>
     <row r="176" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="22" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B176" s="22" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C176" s="3" t="s">
         <v>2785</v>
-      </c>
-      <c r="B176" s="22" t="s">
-        <v>2725</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>2786</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="G176" s="22" t="s">
         <v>2256</v>
@@ -22523,7 +22520,7 @@
         <v>1938</v>
       </c>
       <c r="B177" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>532</v>
@@ -22535,7 +22532,7 @@
         <v>2417</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="G177" s="22" t="s">
         <v>2256</v>
@@ -22543,22 +22540,22 @@
     </row>
     <row r="178" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="22" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>532</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="E178" s="23" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="G178" s="22" t="s">
         <v>2256</v>
@@ -22569,10 +22566,10 @@
         <v>1923</v>
       </c>
       <c r="B179" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>2062</v>
@@ -22592,19 +22589,19 @@
         <v>1920</v>
       </c>
       <c r="B180" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C180" s="3" t="s">
+        <v>2791</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F180" s="3" t="s">
         <v>2792</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>2484</v>
-      </c>
-      <c r="E180" s="23" t="s">
-        <v>2485</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>2793</v>
       </c>
       <c r="G180" s="22" t="s">
         <v>2256</v>
@@ -22615,19 +22612,19 @@
         <v>1979</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C181" s="3" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>2794</v>
       </c>
-      <c r="D181" s="3" t="s">
+      <c r="E181" s="23" t="s">
         <v>2795</v>
       </c>
-      <c r="E181" s="23" t="s">
+      <c r="F181" s="3" t="s">
         <v>2796</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>2797</v>
       </c>
       <c r="G181" s="22" t="s">
         <v>2256</v>
@@ -22638,19 +22635,19 @@
         <v>1981</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E182" s="23" t="s">
+        <v>2798</v>
+      </c>
+      <c r="F182" s="3" t="s">
         <v>2799</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>2800</v>
       </c>
       <c r="G182" s="22" t="s">
         <v>2256</v>
@@ -22661,19 +22658,19 @@
         <v>1957</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C183" s="3" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="E183" s="23" t="s">
         <v>2801</v>
       </c>
-      <c r="D183" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="E183" s="23" t="s">
+      <c r="F183" s="3" t="s">
         <v>2802</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>2803</v>
       </c>
       <c r="G183" s="22" t="s">
         <v>2256</v>
@@ -22684,19 +22681,19 @@
         <v>1970</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="E184" s="23" t="s">
+        <v>2695</v>
+      </c>
+      <c r="F184" s="3" t="s">
         <v>2696</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>2697</v>
       </c>
       <c r="G184" s="22" t="s">
         <v>2256</v>
@@ -22704,22 +22701,22 @@
     </row>
     <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="22" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B185" s="22" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>2805</v>
       </c>
-      <c r="B185" s="22" t="s">
-        <v>2725</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>2806</v>
-      </c>
       <c r="D185" s="3" t="s">
+        <v>2699</v>
+      </c>
+      <c r="E185" s="23" t="s">
         <v>2700</v>
       </c>
-      <c r="E185" s="23" t="s">
+      <c r="F185" s="3" t="s">
         <v>2701</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>2702</v>
       </c>
       <c r="G185" s="22" t="s">
         <v>2256</v>
@@ -22730,10 +22727,10 @@
         <v>1972</v>
       </c>
       <c r="B186" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>2062</v>
@@ -22742,7 +22739,7 @@
         <v>2397</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="G186" s="22" t="s">
         <v>2256</v>
@@ -22753,19 +22750,19 @@
         <v>1936</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E187" s="23" t="s">
+        <v>2809</v>
+      </c>
+      <c r="F187" s="3" t="s">
         <v>2810</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>2811</v>
       </c>
       <c r="G187" s="22" t="s">
         <v>2256</v>
@@ -22776,19 +22773,19 @@
         <v>1925</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E188" s="23" t="s">
+        <v>2812</v>
+      </c>
+      <c r="F188" s="3" t="s">
         <v>2813</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>2814</v>
       </c>
       <c r="G188" s="22" t="s">
         <v>2256</v>
@@ -22799,19 +22796,19 @@
         <v>1933</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E189" s="23" t="s">
+        <v>2815</v>
+      </c>
+      <c r="F189" s="3" t="s">
         <v>2816</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>2817</v>
       </c>
       <c r="G189" s="22" t="s">
         <v>2256</v>
@@ -22819,19 +22816,19 @@
     </row>
     <row r="190" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A190" s="22" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B190" s="22" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C190" s="3" t="s">
         <v>2818</v>
-      </c>
-      <c r="B190" s="22" t="s">
-        <v>2725</v>
-      </c>
-      <c r="C190" s="3" t="s">
-        <v>2819</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>2291</v>
@@ -22842,22 +22839,22 @@
     </row>
     <row r="191" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A191" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B191" s="22" t="s">
         <v>2821</v>
       </c>
-      <c r="B191" s="22" t="s">
+      <c r="C191" s="3" t="s">
         <v>2822</v>
-      </c>
-      <c r="C191" s="3" t="s">
-        <v>2823</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E191" s="23" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F191" s="3" t="s">
         <v>2824</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>2825</v>
       </c>
       <c r="G191" s="22" t="s">
         <v>2256</v>
@@ -22865,10 +22862,10 @@
     </row>
     <row r="192" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A192" s="22" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="B192" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>2009</v>
@@ -22877,10 +22874,10 @@
         <v>2067</v>
       </c>
       <c r="E192" s="23" t="s">
+        <v>2826</v>
+      </c>
+      <c r="F192" s="3" t="s">
         <v>2827</v>
-      </c>
-      <c r="F192" s="3" t="s">
-        <v>2828</v>
       </c>
       <c r="G192" s="22" t="s">
         <v>2256</v>
@@ -22888,22 +22885,22 @@
     </row>
     <row r="193" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A193" s="22" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B193" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>2829</v>
-      </c>
-      <c r="B193" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>2830</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E193" s="23" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F193" s="3" t="s">
         <v>2831</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>2832</v>
       </c>
       <c r="G193" s="22" t="s">
         <v>2256</v>
@@ -22911,10 +22908,10 @@
     </row>
     <row r="194" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A194" s="22" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="B194" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>2014</v>
@@ -22923,10 +22920,10 @@
         <v>2067</v>
       </c>
       <c r="E194" s="23" t="s">
+        <v>2833</v>
+      </c>
+      <c r="F194" s="3" t="s">
         <v>2834</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>2835</v>
       </c>
       <c r="G194" s="22" t="s">
         <v>2256</v>
@@ -22934,19 +22931,19 @@
     </row>
     <row r="195" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A195" s="22" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B195" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C195" s="3" t="s">
         <v>2836</v>
-      </c>
-      <c r="B195" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>2837</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>2291</v>
@@ -22957,22 +22954,22 @@
     </row>
     <row r="196" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A196" s="22" t="s">
+        <v>2838</v>
+      </c>
+      <c r="B196" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C196" s="3" t="s">
         <v>2839</v>
-      </c>
-      <c r="B196" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>2840</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E196" s="23" t="s">
+        <v>2840</v>
+      </c>
+      <c r="F196" s="3" t="s">
         <v>2841</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>2842</v>
       </c>
       <c r="G196" s="22" t="s">
         <v>2256</v>
@@ -22980,10 +22977,10 @@
     </row>
     <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A197" s="22" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>2019</v>
@@ -22992,10 +22989,10 @@
         <v>2067</v>
       </c>
       <c r="E197" s="23" t="s">
+        <v>2843</v>
+      </c>
+      <c r="F197" s="3" t="s">
         <v>2844</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>2845</v>
       </c>
       <c r="G197" s="22" t="s">
         <v>2256</v>
@@ -23003,22 +23000,22 @@
     </row>
     <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A198" s="22" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B198" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>2846</v>
-      </c>
-      <c r="B198" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>2847</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E198" s="23" t="s">
+        <v>2812</v>
+      </c>
+      <c r="F198" s="3" t="s">
         <v>2813</v>
-      </c>
-      <c r="F198" s="3" t="s">
-        <v>2814</v>
       </c>
       <c r="G198" s="22" t="s">
         <v>2256</v>
@@ -23026,13 +23023,13 @@
     </row>
     <row r="199" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A199" s="22" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B199" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>2848</v>
-      </c>
-      <c r="B199" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C199" s="3" t="s">
-        <v>2849</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>2062</v>
@@ -23049,10 +23046,10 @@
     </row>
     <row r="200" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A200" s="22" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="B200" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>532</v>
@@ -23061,10 +23058,10 @@
         <v>2067</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="G200" s="22" t="s">
         <v>2256</v>
@@ -23072,10 +23069,10 @@
     </row>
     <row r="201" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A201" s="22" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>2028</v>
@@ -23084,10 +23081,10 @@
         <v>2067</v>
       </c>
       <c r="E201" s="23" t="s">
+        <v>2851</v>
+      </c>
+      <c r="F201" s="3" t="s">
         <v>2852</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>2853</v>
       </c>
       <c r="G201" s="22" t="s">
         <v>2256</v>
@@ -23095,19 +23092,19 @@
     </row>
     <row r="202" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A202" s="22" t="s">
+        <v>2853</v>
+      </c>
+      <c r="B202" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>2854</v>
-      </c>
-      <c r="B202" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>2855</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E202" s="23" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>2291</v>
@@ -23118,10 +23115,10 @@
     </row>
     <row r="203" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A203" s="22" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>2033</v>
@@ -23130,10 +23127,10 @@
         <v>2067</v>
       </c>
       <c r="E203" s="23" t="s">
+        <v>2857</v>
+      </c>
+      <c r="F203" s="3" t="s">
         <v>2858</v>
-      </c>
-      <c r="F203" s="3" t="s">
-        <v>2859</v>
       </c>
       <c r="G203" s="22" t="s">
         <v>2256</v>
@@ -23141,10 +23138,10 @@
     </row>
     <row r="204" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A204" s="22" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>2033</v>
@@ -23153,7 +23150,7 @@
         <v>2062</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>2291</v>
@@ -23164,10 +23161,10 @@
     </row>
     <row r="205" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A205" s="22" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>2038</v>
@@ -23176,10 +23173,10 @@
         <v>2067</v>
       </c>
       <c r="E205" s="23" t="s">
+        <v>2862</v>
+      </c>
+      <c r="F205" s="3" t="s">
         <v>2863</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>2864</v>
       </c>
       <c r="G205" s="22" t="s">
         <v>2256</v>
@@ -23187,22 +23184,22 @@
     </row>
     <row r="206" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A206" s="22" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B206" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>2865</v>
-      </c>
-      <c r="B206" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>2866</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E206" s="23" t="s">
+        <v>2866</v>
+      </c>
+      <c r="F206" s="3" t="s">
         <v>2867</v>
-      </c>
-      <c r="F206" s="3" t="s">
-        <v>2868</v>
       </c>
       <c r="G206" s="22" t="s">
         <v>2256</v>
@@ -23210,10 +23207,10 @@
     </row>
     <row r="207" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A207" s="22" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>2043</v>
@@ -23222,10 +23219,10 @@
         <v>2067</v>
       </c>
       <c r="E207" s="23" t="s">
+        <v>2869</v>
+      </c>
+      <c r="F207" s="3" t="s">
         <v>2870</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>2871</v>
       </c>
       <c r="G207" s="22" t="s">
         <v>2256</v>
@@ -23233,19 +23230,19 @@
     </row>
     <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A208" s="22" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B208" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C208" s="3" t="s">
         <v>2872</v>
       </c>
-      <c r="B208" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C208" s="3" t="s">
+      <c r="D208" s="3" t="s">
         <v>2873</v>
       </c>
-      <c r="D208" s="3" t="s">
+      <c r="E208" s="23" t="s">
         <v>2874</v>
-      </c>
-      <c r="E208" s="23" t="s">
-        <v>2875</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>2291</v>
@@ -23256,22 +23253,22 @@
     </row>
     <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A209" s="22" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B209" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C209" s="3" t="s">
         <v>2876</v>
-      </c>
-      <c r="B209" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>2877</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>2062</v>
       </c>
       <c r="E209" s="23" t="s">
+        <v>2877</v>
+      </c>
+      <c r="F209" s="3" t="s">
         <v>2878</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>2879</v>
       </c>
       <c r="G209" s="22" t="s">
         <v>2256</v>
@@ -23279,22 +23276,22 @@
     </row>
     <row r="210" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A210" s="22" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B210" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C210" s="3" t="s">
         <v>2880</v>
       </c>
-      <c r="B210" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C210" s="3" t="s">
+      <c r="D210" s="3" t="s">
         <v>2881</v>
       </c>
-      <c r="D210" s="3" t="s">
+      <c r="E210" s="23" t="s">
         <v>2882</v>
       </c>
-      <c r="E210" s="23" t="s">
+      <c r="F210" s="3" t="s">
         <v>2883</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>2884</v>
       </c>
       <c r="G210" s="22" t="s">
         <v>2256</v>
@@ -23302,22 +23299,22 @@
     </row>
     <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A211" s="22" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B211" s="22" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C211" s="3" t="s">
         <v>2885</v>
-      </c>
-      <c r="B211" s="22" t="s">
-        <v>2822</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>2886</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>2093</v>
       </c>
       <c r="E211" s="23" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F211" s="3" t="s">
         <v>2887</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>2888</v>
       </c>
       <c r="G211" s="22" t="s">
         <v>2256</v>
